--- a/data_understanding/collect_data/data/entidad_competicion.xlsx
+++ b/data_understanding/collect_data/data/entidad_competicion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31EE2F61-CF73-C64B-8DED-558948202CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF161B4-8484-9E4D-BF6C-02ED23C77109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{7E04431C-C58B-6A45-9218-66EB9A490B36}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
   <si>
     <t>id_competicion</t>
   </si>
@@ -50,136 +50,247 @@
     <t>pais</t>
   </si>
   <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t>Liga Profesional</t>
-  </si>
-  <si>
-    <t>Copa de la Liga Profesional</t>
-  </si>
-  <si>
-    <t>Copa Argentina</t>
-  </si>
-  <si>
-    <t>Copa de la Superliga</t>
-  </si>
-  <si>
-    <t>Supercopa</t>
-  </si>
-  <si>
-    <t>Supercopa Internacional</t>
-  </si>
-  <si>
-    <t>Trofeo de Campeones</t>
-  </si>
-  <si>
-    <t>Chile</t>
-  </si>
-  <si>
-    <t>Bolivia</t>
-  </si>
-  <si>
-    <t>Liga</t>
-  </si>
-  <si>
-    <t>Copa</t>
-  </si>
-  <si>
-    <t>League Cup</t>
-  </si>
-  <si>
-    <t>Brasileirao Serie A</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>Copa do Brasil</t>
-  </si>
-  <si>
-    <t>Supercopa do Brasil</t>
-  </si>
-  <si>
-    <t>Copa Chile</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t>Primera A</t>
-  </si>
-  <si>
-    <t>Copa Colombia</t>
-  </si>
-  <si>
-    <t>Superliga</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Liga Pro</t>
-  </si>
-  <si>
-    <t>Copa Ecuador</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Copa Paraguay</t>
-  </si>
-  <si>
-    <t>Liga 1</t>
-  </si>
-  <si>
-    <t>Copa Bicentenario</t>
-  </si>
-  <si>
-    <t>Supercopa Peruana</t>
-  </si>
-  <si>
-    <t>Uruguay</t>
-  </si>
-  <si>
-    <t>Copa AUF Uruguay</t>
-  </si>
-  <si>
-    <t>Venezuela</t>
-  </si>
-  <si>
-    <t>Liga FUTVE</t>
-  </si>
-  <si>
-    <t>Copa Venezuela</t>
-  </si>
-  <si>
-    <t>Copa Bicentenaria</t>
-  </si>
-  <si>
-    <t>Copa Libertadores</t>
-  </si>
-  <si>
-    <t>Copa Sudamericana</t>
-  </si>
-  <si>
-    <t>Recopa Sudamericana</t>
-  </si>
-  <si>
-    <t>Sudamerica</t>
-  </si>
-  <si>
-    <t>Division Profesional</t>
-  </si>
-  <si>
-    <t>Copa Peru</t>
-  </si>
-  <si>
-    <t>Peru</t>
-  </si>
-  <si>
-    <t>Primera Division</t>
+    <t>1ligarg</t>
+  </si>
+  <si>
+    <t>liga profesional</t>
+  </si>
+  <si>
+    <t>liga</t>
+  </si>
+  <si>
+    <t>argentina</t>
+  </si>
+  <si>
+    <t>2coparg</t>
+  </si>
+  <si>
+    <t>copa de la liga profesional</t>
+  </si>
+  <si>
+    <t>3coparg</t>
+  </si>
+  <si>
+    <t>copa argentina</t>
+  </si>
+  <si>
+    <t>copa</t>
+  </si>
+  <si>
+    <t>4coparg</t>
+  </si>
+  <si>
+    <t>copa de la superliga</t>
+  </si>
+  <si>
+    <t>5suparg</t>
+  </si>
+  <si>
+    <t>supercopa</t>
+  </si>
+  <si>
+    <t>6suparg</t>
+  </si>
+  <si>
+    <t>supercopa internacional</t>
+  </si>
+  <si>
+    <t>7troarg</t>
+  </si>
+  <si>
+    <t>trofeo de campeones</t>
+  </si>
+  <si>
+    <t>8divbol</t>
+  </si>
+  <si>
+    <t>division profesional</t>
+  </si>
+  <si>
+    <t>bolivia</t>
+  </si>
+  <si>
+    <t>9leabol</t>
+  </si>
+  <si>
+    <t>league cup</t>
+  </si>
+  <si>
+    <t>10brabra</t>
+  </si>
+  <si>
+    <t>brasileirao serie a</t>
+  </si>
+  <si>
+    <t>brasil</t>
+  </si>
+  <si>
+    <t>11copbra</t>
+  </si>
+  <si>
+    <t>copa do brasil</t>
+  </si>
+  <si>
+    <t>12supbra</t>
+  </si>
+  <si>
+    <t>supercopa do brasil</t>
+  </si>
+  <si>
+    <t>13prichi</t>
+  </si>
+  <si>
+    <t>primera division</t>
+  </si>
+  <si>
+    <t>chile</t>
+  </si>
+  <si>
+    <t>14copchi</t>
+  </si>
+  <si>
+    <t>copa chile</t>
+  </si>
+  <si>
+    <t>15supchi</t>
+  </si>
+  <si>
+    <t>16pricol</t>
+  </si>
+  <si>
+    <t>primera a</t>
+  </si>
+  <si>
+    <t>colombia</t>
+  </si>
+  <si>
+    <t>17copcol</t>
+  </si>
+  <si>
+    <t>copa colombia</t>
+  </si>
+  <si>
+    <t>18supcol</t>
+  </si>
+  <si>
+    <t>superliga</t>
+  </si>
+  <si>
+    <t>19ligecu</t>
+  </si>
+  <si>
+    <t>liga pro</t>
+  </si>
+  <si>
+    <t>ecuador</t>
+  </si>
+  <si>
+    <t>20copecu</t>
+  </si>
+  <si>
+    <t>copa ecuador</t>
+  </si>
+  <si>
+    <t>21supecu</t>
+  </si>
+  <si>
+    <t>22pripar</t>
+  </si>
+  <si>
+    <t>paraguay</t>
+  </si>
+  <si>
+    <t>23coppar</t>
+  </si>
+  <si>
+    <t>copa paraguay</t>
+  </si>
+  <si>
+    <t>24suppar</t>
+  </si>
+  <si>
+    <t>25ligper</t>
+  </si>
+  <si>
+    <t>liga 1</t>
+  </si>
+  <si>
+    <t>peru</t>
+  </si>
+  <si>
+    <t>26copper</t>
+  </si>
+  <si>
+    <t>copa bicentenario</t>
+  </si>
+  <si>
+    <t>27copper</t>
+  </si>
+  <si>
+    <t>copa peru</t>
+  </si>
+  <si>
+    <t>28supper</t>
+  </si>
+  <si>
+    <t>supercopa peruana</t>
+  </si>
+  <si>
+    <t>29priuru</t>
+  </si>
+  <si>
+    <t>uruguay</t>
+  </si>
+  <si>
+    <t>30copuru</t>
+  </si>
+  <si>
+    <t>copa auf uruguay</t>
+  </si>
+  <si>
+    <t>31supuru</t>
+  </si>
+  <si>
+    <t>32ligven</t>
+  </si>
+  <si>
+    <t>liga futve</t>
+  </si>
+  <si>
+    <t>venezuela</t>
+  </si>
+  <si>
+    <t>33copven</t>
+  </si>
+  <si>
+    <t>copa venezuela</t>
+  </si>
+  <si>
+    <t>34copven</t>
+  </si>
+  <si>
+    <t>copa bicentenaria</t>
+  </si>
+  <si>
+    <t>35copsud</t>
+  </si>
+  <si>
+    <t>copa libertadores</t>
+  </si>
+  <si>
+    <t>sudamerica</t>
+  </si>
+  <si>
+    <t>36copsud</t>
+  </si>
+  <si>
+    <t>copa sudamericana</t>
+  </si>
+  <si>
+    <t>37recsud</t>
+  </si>
+  <si>
+    <t>recopa sudamericana</t>
   </si>
 </sst>
 </file>
@@ -215,12 +326,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -558,558 +665,521 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="str">
-        <f>1&amp;LEFT(B2,3)&amp;LEFT(D2,3)</f>
-        <v>1LigArg</v>
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="str">
-        <f>2&amp;LEFT(B3,3)&amp;LEFT(D3,3)</f>
-        <v>2CopArg</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="str">
-        <f>3&amp;LEFT(B4,3)&amp;LEFT(D4,3)</f>
-        <v>3CopArg</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="str">
-        <f>4&amp;LEFT(B5,3)&amp;LEFT(D5,3)</f>
-        <v>4CopArg</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="str">
-        <f>5&amp;LEFT(B6,3)&amp;LEFT(D6,3)</f>
-        <v>5SupArg</v>
-      </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="str">
-        <f>6&amp;LEFT(B7,3)&amp;LEFT(D7,3)</f>
-        <v>6SupArg</v>
+      <c r="A7" t="s">
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="str">
-        <f>7&amp;LEFT(B8,3)&amp;LEFT(D8,3)</f>
-        <v>7TroArg</v>
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="str">
-        <f>8&amp;LEFT(B9,3)&amp;LEFT(D9,3)</f>
-        <v>8DivBol</v>
+      <c r="A9" t="s">
+        <v>21</v>
       </c>
       <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="str">
-        <f>9&amp;LEFT(B10,3)&amp;LEFT(D10,3)</f>
-        <v>9LeaBol</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="str">
-        <f>10&amp;LEFT(B11,3)&amp;LEFT(D11,3)</f>
-        <v>10BraBra</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="str">
-        <f>11&amp;LEFT(B12,3)&amp;LEFT(D12,3)</f>
-        <v>11CopBra</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="str">
-        <f>12&amp;LEFT(B13,3)&amp;LEFT(D13,3)</f>
-        <v>12SupBra</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="str">
-        <f>13&amp;LEFT(B14,3)&amp;LEFT(D14,3)</f>
-        <v>13PriChi</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="str">
-        <f>14&amp;LEFT(B15,3)&amp;LEFT(D15,3)</f>
-        <v>14CopChi</v>
-      </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="str">
-        <f>15&amp;LEFT(B16,3)&amp;LEFT(D16,3)</f>
-        <v>15SupChi</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="str">
-        <f>16&amp;LEFT(B17,3)&amp;LEFT(D17,3)</f>
-        <v>16PriCol</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="str">
-        <f>17&amp;LEFT(B18,3)&amp;LEFT(D18,3)</f>
-        <v>17CopCol</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="str">
-        <f>18&amp;LEFT(B19,3)&amp;LEFT(D19,3)</f>
-        <v>18SupCol</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="str">
-        <f>19&amp;LEFT(B20,3)&amp;LEFT(D20,3)</f>
-        <v>19LigEcu</v>
-      </c>
-      <c r="B20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="str">
-        <f>20&amp;LEFT(B21,3)&amp;LEFT(D21,3)</f>
-        <v>20CopEcu</v>
-      </c>
-      <c r="B21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="str">
-        <f>21&amp;LEFT(B22,3)&amp;LEFT(D22,3)</f>
-        <v>21SupEcu</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" t="str">
-        <f>22&amp;LEFT(B23,3)&amp;LEFT(D23,3)</f>
-        <v>22PriPar</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" t="str">
-        <f>23&amp;LEFT(B24,3)&amp;LEFT(D24,3)</f>
-        <v>23CopPar</v>
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" t="str">
-        <f>24&amp;LEFT(B25,3)&amp;LEFT(D25,3)</f>
-        <v>24SupPar</v>
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="str">
-        <f>25&amp;LEFT(B26,3)&amp;LEFT(D26,3)</f>
-        <v>25LigPer</v>
+      <c r="A26" t="s">
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="str">
-        <f>26&amp;LEFT(B27,3)&amp;LEFT(D27,3)</f>
-        <v>26CopPer</v>
+      <c r="A27" t="s">
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="str">
-        <f>27&amp;LEFT(B28,3)&amp;LEFT(D28,3)</f>
-        <v>27CopPer</v>
+      <c r="A28" t="s">
+        <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="str">
-        <f>28&amp;LEFT(B29,3)&amp;LEFT(D29,3)</f>
-        <v>28SupPer</v>
+      <c r="A29" t="s">
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="str">
-        <f>29&amp;LEFT(B30,3)&amp;LEFT(D30,3)</f>
-        <v>29PriUru</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" t="str">
-        <f>30&amp;LEFT(B31,3)&amp;LEFT(D31,3)</f>
-        <v>30CopUru</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>35</v>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="str">
-        <f>31&amp;LEFT(B32,3)&amp;LEFT(D32,3)</f>
-        <v>31SupUru</v>
+      <c r="A32" t="s">
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="str">
-        <f>32&amp;LEFT(B33,3)&amp;LEFT(D33,3)</f>
-        <v>32LigVen</v>
+      <c r="A33" t="s">
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="str">
-        <f>33&amp;LEFT(B34,3)&amp;LEFT(D34,3)</f>
-        <v>33CopVen</v>
+      <c r="A34" t="s">
+        <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="str">
-        <f>34&amp;LEFT(B35,3)&amp;LEFT(D35,3)</f>
-        <v>34CopVen</v>
+      <c r="A35" t="s">
+        <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="str">
-        <f>35&amp;LEFT(B36,3)&amp;LEFT(D36,3)</f>
-        <v>35CopSud</v>
+      <c r="A36" t="s">
+        <v>78</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="str">
-        <f>36&amp;LEFT(B37,3)&amp;LEFT(D37,3)</f>
-        <v>36CopSud</v>
+      <c r="A37" t="s">
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="str">
-        <f>37&amp;LEFT(B38,3)&amp;LEFT(D38,3)</f>
-        <v>37RecSud</v>
+      <c r="A38" t="s">
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
